--- a/marketing_report/outputs/Cursos/Analisis_No_Matcheados/datos_analisis_no_matcheados.xlsx
+++ b/marketing_report/outputs/Cursos/Analisis_No_Matcheados/datos_analisis_no_matcheados.xlsx
@@ -8,16 +8,14 @@
   </bookViews>
   <sheets>
     <sheet name="Distribucion_Consultas" sheetId="1" r:id="rId1"/>
-    <sheet name="Tiempos_Resolucion" sheetId="2" r:id="rId2"/>
-    <sheet name="Deciles_Tiempos" sheetId="3" r:id="rId3"/>
-    <sheet name="Dominios" sheetId="4" r:id="rId4"/>
+    <sheet name="Dominios" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
   <si>
     <t>Rango</t>
   </si>
@@ -67,102 +65,6 @@
     <t>10+ consultas</t>
   </si>
   <si>
-    <t>Metrica</t>
-  </si>
-  <si>
-    <t>Valor</t>
-  </si>
-  <si>
-    <t>Promedio</t>
-  </si>
-  <si>
-    <t>Mediana</t>
-  </si>
-  <si>
-    <t>Moda</t>
-  </si>
-  <si>
-    <t>Personas Analizadas</t>
-  </si>
-  <si>
-    <t>91 días</t>
-  </si>
-  <si>
-    <t>31 días</t>
-  </si>
-  <si>
-    <t>1 días</t>
-  </si>
-  <si>
-    <t>181</t>
-  </si>
-  <si>
-    <t>Decil</t>
-  </si>
-  <si>
-    <t>Dias</t>
-  </si>
-  <si>
-    <t>D10</t>
-  </si>
-  <si>
-    <t>D20</t>
-  </si>
-  <si>
-    <t>D30</t>
-  </si>
-  <si>
-    <t>D40</t>
-  </si>
-  <si>
-    <t>D50 (Mediana)</t>
-  </si>
-  <si>
-    <t>D60</t>
-  </si>
-  <si>
-    <t>D70</t>
-  </si>
-  <si>
-    <t>D80</t>
-  </si>
-  <si>
-    <t>D90</t>
-  </si>
-  <si>
-    <t>D100 (Máx)</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>31</t>
-  </si>
-  <si>
-    <t>67</t>
-  </si>
-  <si>
-    <t>156</t>
-  </si>
-  <si>
-    <t>191</t>
-  </si>
-  <si>
-    <t>251</t>
-  </si>
-  <si>
-    <t>325</t>
-  </si>
-  <si>
     <t>Domain</t>
   </si>
   <si>
@@ -178,55 +80,16 @@
     <t>Tasa_Inscripcion_%</t>
   </si>
   <si>
-    <t>gail.com</t>
-  </si>
-  <si>
-    <t>gamil.com</t>
-  </si>
-  <si>
-    <t>gmai.com</t>
-  </si>
-  <si>
-    <t>gmaiil.com</t>
-  </si>
-  <si>
     <t>gmail.com</t>
   </si>
   <si>
-    <t>gmail.com.ar</t>
-  </si>
-  <si>
-    <t>gmail.con</t>
-  </si>
-  <si>
     <t>hotmail.com</t>
   </si>
   <si>
     <t>hotmail.com.ar</t>
   </si>
   <si>
-    <t>icloud.com</t>
-  </si>
-  <si>
-    <t>live.com</t>
-  </si>
-  <si>
-    <t>live.com.ar</t>
-  </si>
-  <si>
-    <t>mail.com</t>
-  </si>
-  <si>
-    <t>outlook.com</t>
-  </si>
-  <si>
     <t>ucasal.edu.ar</t>
-  </si>
-  <si>
-    <t>yahoo.com</t>
-  </si>
-  <si>
-    <t>inf</t>
   </si>
 </sst>
 </file>
@@ -609,13 +472,13 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>274</v>
+        <v>10</v>
       </c>
       <c r="C2">
-        <v>71.5</v>
+        <v>58.8</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -626,10 +489,10 @@
         <v>6</v>
       </c>
       <c r="B3">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="C3">
-        <v>18.5</v>
+        <v>23.5</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -643,10 +506,10 @@
         <v>7</v>
       </c>
       <c r="B4">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="C4">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -660,10 +523,10 @@
         <v>8</v>
       </c>
       <c r="B5">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>2.3</v>
+        <v>11.8</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -677,10 +540,10 @@
         <v>9</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -694,10 +557,10 @@
         <v>10</v>
       </c>
       <c r="B7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -711,10 +574,10 @@
         <v>11</v>
       </c>
       <c r="B8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -779,10 +642,10 @@
         <v>15</v>
       </c>
       <c r="B12">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -798,444 +661,92 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>32</v>
-      </c>
-      <c r="B6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B7" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" t="s">
-        <v>34</v>
-      </c>
-      <c r="B8" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="s">
-        <v>36</v>
-      </c>
-      <c r="B10" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" t="s">
-        <v>37</v>
-      </c>
-      <c r="B11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>17</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>51</v>
+        <v>19</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>52</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="B2">
-        <v>1</v>
+        <v>28</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2">
-        <v>200</v>
+        <v>125</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="B3">
         <v>2</v>
       </c>
       <c r="C3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
       <c r="E4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="B5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
         <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" t="s">
-        <v>57</v>
-      </c>
-      <c r="B6">
-        <v>524</v>
-      </c>
-      <c r="C6">
-        <v>851</v>
-      </c>
-      <c r="D6">
-        <v>22</v>
-      </c>
-      <c r="E6">
-        <v>162.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" t="s">
-        <v>59</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9">
-        <v>31</v>
-      </c>
-      <c r="C9">
-        <v>44</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>141.94</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" t="s">
-        <v>61</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-      <c r="C10">
-        <v>5</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>62</v>
-      </c>
-      <c r="B11">
-        <v>7</v>
-      </c>
-      <c r="C11">
-        <v>11</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>157.14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-      <c r="E12">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-      <c r="E13">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" t="s">
-        <v>65</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <v>2</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" t="s">
-        <v>66</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" t="s">
-        <v>67</v>
-      </c>
-      <c r="B16">
-        <v>12</v>
-      </c>
-      <c r="C16">
-        <v>12</v>
-      </c>
-      <c r="D16">
-        <v>0</v>
-      </c>
-      <c r="E16">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" t="s">
-        <v>68</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-      <c r="E17" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/marketing_report/outputs/Cursos/Analisis_No_Matcheados/datos_analisis_no_matcheados.xlsx
+++ b/marketing_report/outputs/Cursos/Analisis_No_Matcheados/datos_analisis_no_matcheados.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Rango</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>ucasal.edu.ar</t>
+  </si>
+  <si>
+    <t>inf</t>
   </si>
 </sst>
 </file>
@@ -472,13 +475,13 @@
         <v>5</v>
       </c>
       <c r="B2">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C2">
-        <v>58.8</v>
+        <v>46.2</v>
       </c>
       <c r="D2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E2">
         <v>100</v>
@@ -492,7 +495,7 @@
         <v>4</v>
       </c>
       <c r="C3">
-        <v>23.5</v>
+        <v>30.8</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -509,7 +512,7 @@
         <v>1</v>
       </c>
       <c r="C4">
-        <v>5.9</v>
+        <v>7.7</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -526,7 +529,7 @@
         <v>2</v>
       </c>
       <c r="C5">
-        <v>11.8</v>
+        <v>15.4</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -686,16 +689,16 @@
         <v>21</v>
       </c>
       <c r="B2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2">
-        <v>125</v>
+        <v>122.22</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -703,16 +706,16 @@
         <v>22</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3">
-        <v>150</v>
+      <c r="E3" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:5">
